--- a/output/Data and Chart Outputs/taiwan_live_daily.xlsx
+++ b/output/Data and Chart Outputs/taiwan_live_daily.xlsx
@@ -456,7 +456,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -471,7 +470,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>

--- a/output/Data and Chart Outputs/taiwan_live_daily.xlsx
+++ b/output/Data and Chart Outputs/taiwan_live_daily.xlsx
@@ -456,6 +456,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -470,6 +471,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -495,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,6 +745,102 @@
       <c r="AD2" t="inlineStr">
         <is>
           <t>2026-10-10T10:10:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13.966</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.5737</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.5693</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5259</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9364</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.1514</v>
+      </c>
+      <c r="P3" t="n">
+        <v>27.0268</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>13029.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>936.4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6422.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1151.4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>661.8</v>
+      </c>
+      <c r="V3" t="n">
+        <v>172.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3569.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>525.9</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>520</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-10-11T00:10:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2026-10-11T00:10:00</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/taiwan_live_daily.xlsx
+++ b/output/Data and Chart Outputs/taiwan_live_daily.xlsx
@@ -456,6 +456,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -470,6 +471,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -751,85 +753,85 @@
         <v>46306</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>13.966</v>
+        <v>13.1852</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5737</v>
+        <v>7.057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6956</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1724</v>
+        <v>0.1703</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.6418</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5693</v>
+        <v>3.4322</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5259</v>
+        <v>0.4748</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0377</v>
+        <v>0.0382</v>
       </c>
       <c r="L3" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0112</v>
+        <v>-0.2736</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9364</v>
+        <v>0.4682</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1514</v>
+        <v>1.1232</v>
       </c>
       <c r="P3" t="n">
-        <v>27.0268</v>
+        <v>25.9551</v>
       </c>
       <c r="Q3" t="n">
-        <v>13029.6</v>
+        <v>25434</v>
       </c>
       <c r="R3" t="n">
         <v>936.4</v>
       </c>
       <c r="S3" t="n">
-        <v>6422.3</v>
+        <v>11867.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1151.4</v>
+        <v>2246.5</v>
       </c>
       <c r="U3" t="n">
-        <v>661.8</v>
+        <v>1391.1</v>
       </c>
       <c r="V3" t="n">
-        <v>172.4</v>
+        <v>340.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1283.634</v>
       </c>
       <c r="X3" t="n">
-        <v>3569.3</v>
+        <v>6864.400000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>525.9</v>
+        <v>949.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>37.7</v>
+        <v>76.5</v>
       </c>
       <c r="AA3" t="n">
         <v>520</v>
       </c>
       <c r="AB3" t="n">
-        <v>-11.2</v>
+        <v>-547.1</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -838,7 +840,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2026-10-11T00:10:00</t>
+          <t>2026-10-11T07:10:00</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/taiwan_live_daily.xlsx
+++ b/output/Data and Chart Outputs/taiwan_live_daily.xlsx
@@ -753,85 +753,85 @@
         <v>46306</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>13.1852</v>
+        <v>12.572</v>
       </c>
       <c r="E3" t="n">
-        <v>7.057</v>
+        <v>6.8846</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6956</v>
+        <v>0.7093</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1703</v>
+        <v>0.169</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6418</v>
+        <v>1.8067</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4322</v>
+        <v>3.3915</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4748</v>
+        <v>0.4355</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0382</v>
+        <v>0.0392</v>
       </c>
       <c r="L3" t="n">
-        <v>0.26</v>
+        <v>0.1733</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2736</v>
+        <v>-0.6031</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4682</v>
+        <v>0.3121</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1232</v>
+        <v>1.1148</v>
       </c>
       <c r="P3" t="n">
-        <v>25.9551</v>
+        <v>26.1811</v>
       </c>
       <c r="Q3" t="n">
-        <v>25434</v>
+        <v>36779.7</v>
       </c>
       <c r="R3" t="n">
         <v>936.4</v>
       </c>
       <c r="S3" t="n">
-        <v>11867.6</v>
+        <v>17309.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2246.5</v>
+        <v>3344.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1391.1</v>
+        <v>2127.8</v>
       </c>
       <c r="V3" t="n">
-        <v>340.5</v>
+        <v>506.9</v>
       </c>
       <c r="W3" t="n">
-        <v>1283.634</v>
+        <v>5420.055</v>
       </c>
       <c r="X3" t="n">
-        <v>6864.400000000001</v>
+        <v>10174.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>949.5</v>
+        <v>1306.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>76.5</v>
+        <v>117.7</v>
       </c>
       <c r="AA3" t="n">
         <v>520</v>
       </c>
       <c r="AB3" t="n">
-        <v>-547.1</v>
+        <v>-1809.4</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2026-10-11T07:10:00</t>
+          <t>2026-10-11T08:20:00</t>
         </is>
       </c>
     </row>
